--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.05338521076716</v>
+        <v>6.183675096749663</v>
       </c>
       <c r="D2" t="n">
-        <v>26.47985303335475</v>
+        <v>4.302976117920148</v>
       </c>
       <c r="E2" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F2" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.75918758951882</v>
+        <v>6.948367983296808</v>
       </c>
       <c r="D3" t="n">
-        <v>44.39573602923978</v>
+        <v>7.214307104751464</v>
       </c>
       <c r="E3" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F3" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.5892482620873</v>
+        <v>4.158252842589187</v>
       </c>
       <c r="D4" t="n">
-        <v>23.53645794523275</v>
+        <v>3.824674416100322</v>
       </c>
       <c r="E4" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F4" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.86715219683895</v>
+        <v>4.203412231986329</v>
       </c>
       <c r="D5" t="n">
-        <v>25.51732528514734</v>
+        <v>4.146565358836443</v>
       </c>
       <c r="E5" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F5" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.11494850123171</v>
+        <v>6.193679131450152</v>
       </c>
       <c r="D6" t="n">
-        <v>38.05731890046812</v>
+        <v>6.184314321326069</v>
       </c>
       <c r="E6" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F6" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.35966921501762</v>
+        <v>5.745946247440363</v>
       </c>
       <c r="D7" t="n">
-        <v>33.20471126162538</v>
+        <v>5.395765580014124</v>
       </c>
       <c r="E7" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F7" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.24074651804568</v>
+        <v>2.151621309182424</v>
       </c>
       <c r="D8" t="n">
-        <v>12.59240560232205</v>
+        <v>2.046265910377334</v>
       </c>
       <c r="E8" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F8" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.00740651096645</v>
+        <v>2.438703558032049</v>
       </c>
       <c r="D9" t="n">
-        <v>15.54052658466284</v>
+        <v>2.525335570007712</v>
       </c>
       <c r="E9" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F9" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>15.25103269249127</v>
+        <v>2.478292812529832</v>
       </c>
       <c r="D10" t="n">
-        <v>16.45706129042131</v>
+        <v>2.674272459693463</v>
       </c>
       <c r="E10" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F10" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>30.29408035467119</v>
+        <v>4.922788057634068</v>
       </c>
       <c r="D11" t="n">
-        <v>24.47702863215224</v>
+        <v>3.97751715272474</v>
       </c>
       <c r="E11" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F11" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.32995601631912</v>
+        <v>5.578617852651858</v>
       </c>
       <c r="D12" t="n">
-        <v>10.95642834353521</v>
+        <v>1.780419605824472</v>
       </c>
       <c r="E12" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F12" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.44537655556857</v>
+        <v>6.734873690279893</v>
       </c>
       <c r="D13" t="n">
-        <v>42.84327875959497</v>
+        <v>6.962032798434183</v>
       </c>
       <c r="E13" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F13" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.07319402339069</v>
+        <v>1.636894028800988</v>
       </c>
       <c r="D14" t="n">
-        <v>33.8452429942614</v>
+        <v>5.499851986567479</v>
       </c>
       <c r="E14" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F14" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.922867050546518</v>
+        <v>1.449965895713809</v>
       </c>
       <c r="D15" t="n">
-        <v>48.43002747293566</v>
+        <v>7.869879464352044</v>
       </c>
       <c r="E15" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F15" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.19610940837051</v>
+        <v>5.394367778860208</v>
       </c>
       <c r="D16" t="n">
-        <v>58.86949858389652</v>
+        <v>9.566293519883185</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43948685097065</v>
+        <v>1.858916613282731</v>
       </c>
       <c r="F16" t="n">
-        <v>13.65383605210014</v>
+        <v>2.218748358466273</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
